--- a/pds_admin_karnataka/Backend/Backend/Result_Sheet_F1.xlsx
+++ b/pds_admin_karnataka/Backend/Backend/Result_Sheet_F1.xlsx
@@ -103,28 +103,34 @@
     <t>FPS</t>
   </si>
   <si>
+    <t>FPS1</t>
+  </si>
+  <si>
     <t>FPS2</t>
   </si>
   <si>
     <t>FPS4</t>
   </si>
   <si>
+    <t>FPS5</t>
+  </si>
+  <si>
+    <t>FPS6</t>
+  </si>
+  <si>
+    <t>FPS7</t>
+  </si>
+  <si>
     <t>FPS8</t>
   </si>
   <si>
-    <t>FPS5</t>
-  </si>
-  <si>
     <t>FPS9</t>
   </si>
   <si>
-    <t>FPS1</t>
-  </si>
-  <si>
-    <t>FPS6</t>
-  </si>
-  <si>
-    <t>FPS7</t>
+    <t>Yavatmal Yass</t>
+  </si>
+  <si>
+    <t>Gram Mandal Maninagar</t>
   </si>
   <si>
     <t>MAHAKUTESHWAR YUVAKA MANDAL YANKANCHI</t>
@@ -133,25 +139,19 @@
     <t>L.B. NAIKAR. KHANAPUR.S.K. 68 (C)(RADDERTIMMAPUR)</t>
   </si>
   <si>
+    <t>YUVAKA MANDAL HAVALAKOD</t>
+  </si>
+  <si>
+    <t>MARUTI YUVAKA MANDAL FAKIRBUDIHAL</t>
+  </si>
+  <si>
+    <t>YUVAKA MANDAL SAGANUR</t>
+  </si>
+  <si>
     <t>YUVAKA MANDAL CHINCHALAKATTI</t>
   </si>
   <si>
-    <t>YUVAKA MANDAL HAVALAKOD</t>
-  </si>
-  <si>
     <t>K.K.LAMANI CHINCHALAKATTI L.T.</t>
-  </si>
-  <si>
-    <t>Yavatmal Yass</t>
-  </si>
-  <si>
-    <t>Gram Mandal Maninagar</t>
-  </si>
-  <si>
-    <t>MARUTI YUVAKA MANDAL FAKIRBUDIHAL</t>
-  </si>
-  <si>
-    <t>YUVAKA MANDAL SAGANUR</t>
   </si>
   <si>
     <t>FRice</t>
@@ -611,8 +611,8 @@
       <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
+      <c r="K2">
+        <v>4</v>
       </c>
       <c r="L2" t="s">
         <v>37</v>
@@ -627,7 +627,7 @@
         <v>24</v>
       </c>
       <c r="P2">
-        <v>16.0227</v>
+        <v>16.0238</v>
       </c>
       <c r="Q2">
         <v>75.6052</v>
@@ -636,10 +636,10 @@
         <v>46</v>
       </c>
       <c r="S2">
-        <v>75.34</v>
+        <v>677</v>
       </c>
       <c r="T2">
-        <v>1691.1721</v>
+        <v>1691.2111</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -674,7 +674,7 @@
         <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
         <v>38</v>
@@ -689,19 +689,19 @@
         <v>24</v>
       </c>
       <c r="P3">
-        <v>15.9938</v>
+        <v>16.0238</v>
       </c>
       <c r="Q3">
-        <v>75.452</v>
+        <v>75.6052</v>
       </c>
       <c r="R3" t="s">
         <v>46</v>
       </c>
       <c r="S3">
-        <v>110.89</v>
+        <v>46.46</v>
       </c>
       <c r="T3">
-        <v>1697.5976</v>
+        <v>1691.2111</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -736,7 +736,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s">
         <v>39</v>
@@ -751,19 +751,19 @@
         <v>24</v>
       </c>
       <c r="P4">
-        <v>16.023</v>
+        <v>16.0227</v>
       </c>
       <c r="Q4">
-        <v>75.4657</v>
+        <v>75.6052</v>
       </c>
       <c r="R4" t="s">
         <v>46</v>
       </c>
       <c r="S4">
-        <v>58.13</v>
+        <v>75.34</v>
       </c>
       <c r="T4">
-        <v>1694.0386</v>
+        <v>1691.1721</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -780,13 +780,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>260017370006</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5">
         <v>27.89</v>
@@ -798,7 +798,7 @@
         <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
         <v>40</v>
@@ -813,19 +813,19 @@
         <v>24</v>
       </c>
       <c r="P5">
-        <v>16.0257</v>
+        <v>15.9938</v>
       </c>
       <c r="Q5">
-        <v>75.45229999999999</v>
+        <v>75.452</v>
       </c>
       <c r="R5" t="s">
         <v>46</v>
       </c>
       <c r="S5">
-        <v>55.51</v>
+        <v>110.89</v>
       </c>
       <c r="T5">
-        <v>1697.0919</v>
+        <v>1697.5976</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -860,7 +860,7 @@
         <v>28</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
         <v>41</v>
@@ -875,19 +875,19 @@
         <v>24</v>
       </c>
       <c r="P6">
-        <v>16.0242</v>
+        <v>16.0257</v>
       </c>
       <c r="Q6">
-        <v>75.4815</v>
+        <v>75.45229999999999</v>
       </c>
       <c r="R6" t="s">
         <v>46</v>
       </c>
       <c r="S6">
-        <v>38.08</v>
+        <v>55.51</v>
       </c>
       <c r="T6">
-        <v>1692.1932</v>
+        <v>1697.0919</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -904,10 +904,10 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
@@ -921,8 +921,8 @@
       <c r="J7" t="s">
         <v>28</v>
       </c>
-      <c r="K7">
-        <v>4</v>
+      <c r="K7" t="s">
+        <v>33</v>
       </c>
       <c r="L7" t="s">
         <v>42</v>
@@ -937,19 +937,19 @@
         <v>24</v>
       </c>
       <c r="P7">
-        <v>16.0238</v>
+        <v>16.0502</v>
       </c>
       <c r="Q7">
-        <v>75.6052</v>
+        <v>75.47539999999999</v>
       </c>
       <c r="R7" t="s">
         <v>46</v>
       </c>
       <c r="S7">
-        <v>677</v>
+        <v>37.54</v>
       </c>
       <c r="T7">
-        <v>1691.2111</v>
+        <v>1697.2908</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -966,10 +966,10 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -999,19 +999,19 @@
         <v>24</v>
       </c>
       <c r="P8">
-        <v>16.0238</v>
+        <v>16.0437</v>
       </c>
       <c r="Q8">
-        <v>75.6052</v>
+        <v>75.474</v>
       </c>
       <c r="R8" t="s">
         <v>46</v>
       </c>
       <c r="S8">
-        <v>46.46</v>
+        <v>27.24</v>
       </c>
       <c r="T8">
-        <v>1691.2111</v>
+        <v>1696.592</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1028,10 +1028,10 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -1061,19 +1061,19 @@
         <v>24</v>
       </c>
       <c r="P9">
-        <v>16.0502</v>
+        <v>16.023</v>
       </c>
       <c r="Q9">
-        <v>75.47539999999999</v>
+        <v>75.4657</v>
       </c>
       <c r="R9" t="s">
         <v>46</v>
       </c>
       <c r="S9">
-        <v>37.54</v>
+        <v>58.13</v>
       </c>
       <c r="T9">
-        <v>1697.2908</v>
+        <v>1694.0386</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1090,10 +1090,10 @@
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
@@ -1123,19 +1123,19 @@
         <v>24</v>
       </c>
       <c r="P10">
-        <v>16.0437</v>
+        <v>16.0242</v>
       </c>
       <c r="Q10">
-        <v>75.474</v>
+        <v>75.4815</v>
       </c>
       <c r="R10" t="s">
         <v>46</v>
       </c>
       <c r="S10">
-        <v>27.24</v>
+        <v>38.08</v>
       </c>
       <c r="T10">
-        <v>1696.592</v>
+        <v>1692.1932</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1155,10 +1155,10 @@
         <v>24</v>
       </c>
       <c r="F11">
-        <v>26001737000</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11">
         <v>27.89</v>
@@ -1173,7 +1173,7 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
         <v>22</v>
